--- a/output/pdf_financials_xlsx/FVL.xlsx
+++ b/output/pdf_financials_xlsx/FVL.xlsx
@@ -6252,49 +6252,49 @@
         <v>5.497508</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>5.961508</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>10.890451</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>10.064257</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>12.763913</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>17.092416</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>11.532588</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>15.138848</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>16.158672</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>16.677246</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>17.312208</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>34.219347</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>31.087666</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>37.071327</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>35.703992</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>39.118442</v>
       </c>
     </row>
     <row r="93">
@@ -10217,7 +10217,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -15062,7 +15066,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -17814,7 +17822,11 @@
           <t>Reserves 15,138,848 12,151,559</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -20062,7 +20074,11 @@
           <t>Reserves 10,064,257 12,719,244</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -22595,7 +22611,11 @@
           <t>Reserves 13,191,016</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FVL.xlsx
+++ b/output/pdf_financials_xlsx/FVL.xlsx
@@ -1101,49 +1101,49 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000171</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.02381</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.017855</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.016545</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002602</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.002537</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.010751</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.007643</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.001773</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.015458</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.08780300000000001</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.066039</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.220665</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.16568</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.503976</v>
       </c>
     </row>
     <row r="13">
@@ -2107,49 +2107,49 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.445618</v>
+        <v>-2.445789</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.179526</v>
+        <v>-5.203336</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.936931</v>
+        <v>-5.954786</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.808855</v>
+        <v>-1.8254</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-7.755822</v>
+        <v>-7.758424</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.960515</v>
+        <v>-0.963052</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.934716</v>
+        <v>-0.9454669999999999</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.338535</v>
+        <v>-0.346178</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.760981</v>
+        <v>-0.762754</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.347444</v>
+        <v>-0.362902</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.207119</v>
+        <v>-2.294922</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.80296</v>
+        <v>-0.868999</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.09712</v>
+        <v>-3.317785</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.089507</v>
+        <v>-1.255187</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-7.344002</v>
+        <v>-7.847978</v>
       </c>
     </row>
     <row r="28">
@@ -2231,49 +2231,49 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.445618</v>
+        <v>-2.445789</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.179526</v>
+        <v>-5.203336</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.912995</v>
+        <v>-5.93085</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.790917</v>
+        <v>-1.807462</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-7.740002</v>
+        <v>-7.742604</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.948923</v>
+        <v>-0.95146</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.923916</v>
+        <v>-0.934667</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.328792</v>
+        <v>-0.336435</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.752812</v>
+        <v>-0.754585</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.290528</v>
+        <v>-0.305986</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.143571</v>
+        <v>-2.231374</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.6993239999999999</v>
+        <v>-0.765363</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.031108</v>
+        <v>-3.251773</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.032839</v>
+        <v>-1.198519</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-7.276342</v>
+        <v>-7.780318</v>
       </c>
     </row>
     <row r="30">
@@ -48458,7 +48458,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -54037,7 +54037,7 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -56546,7 +56546,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">

--- a/output/pdf_financials_xlsx/FVL.xlsx
+++ b/output/pdf_financials_xlsx/FVL.xlsx
@@ -7394,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.425604</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -46632,7 +46632,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FVL.xlsx
+++ b/output/pdf_financials_xlsx/FVL.xlsx
@@ -564,15 +564,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -636,15 +632,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -698,15 +690,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -770,21 +758,17 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.237555</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.181298</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.053072</v>
+        <v>0.075072</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.220322</v>
+        <v>0.223322</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0.333816</v>
@@ -832,15 +816,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -894,15 +874,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.252046</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.110042</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0.07147000000000001</v>
@@ -956,15 +932,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>2.31641</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>4.029729</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1.063419</v>
@@ -1018,15 +990,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-2.31641</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-1.588263</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-1.382199</v>
@@ -1090,15 +1058,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0.035292</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.000213</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.000171</v>
@@ -1152,15 +1116,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1214,15 +1174,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -1276,15 +1232,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>-1.173327</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1.519418</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0.06680700000000001</v>
@@ -1338,15 +1290,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-5.165861</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-5.617992</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-2.445618</v>
@@ -1400,15 +1348,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1646,15 +1590,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-5.165861</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-5.617992</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-2.445618</v>
@@ -1708,15 +1648,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1770,15 +1706,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -1890,15 +1822,11 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-0.47</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>-0.13</v>
@@ -1952,15 +1880,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.47</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>-0.13</v>
@@ -2014,15 +1938,11 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>64.573262</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>11.953174</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>18.812446</v>
@@ -2096,15 +2016,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-5.201153</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-5.618205</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-2.445789</v>
@@ -2158,15 +2074,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -2220,15 +2132,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-5.201153</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-5.618205</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-2.445789</v>
@@ -2374,15 +2282,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -7281,49 +7185,49 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.003942</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.007851</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.018238</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.019588</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.021086</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.017998</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.008629</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.008996000000000001</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.009377999999999999</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.010766</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.005806</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.006255</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.012898</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.014302</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.010407</v>
       </c>
     </row>
     <row r="111">
@@ -7369,10 +7273,10 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.095612</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.07623099999999999</v>
       </c>
       <c r="P111" s="3" t="n">
         <v>0</v>
@@ -8737,10 +8641,10 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.095612</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.07623099999999999</v>
       </c>
       <c r="P134" s="3" t="n">
         <v>0</v>
@@ -8795,10 +8699,10 @@
         <v>0.006437</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-0.329991</v>
+        <v>-0.425603</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>-1.080537</v>
+        <v>-1.156768</v>
       </c>
       <c r="P135" s="3" t="n">
         <v>-0.962721</v>
@@ -8821,7 +8725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U532"/>
+  <dimension ref="A1:U565"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -30100,7 +30004,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -32549,7 +32457,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -36483,7 +36395,11 @@
           <t>Accretion 18,238</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -47536,15 +47452,11 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E394" s="5" t="n">
+        <v>0.057089</v>
+      </c>
+      <c r="F394" s="5" t="n">
+        <v>0.031782</v>
       </c>
       <c r="G394" s="5" t="n">
         <v>0.037667</v>
@@ -47708,15 +47620,11 @@
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
-      <c r="E396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E396" s="5" t="n">
+        <v>0.233051</v>
+      </c>
+      <c r="F396" s="5" t="n">
+        <v>0.07688200000000001</v>
       </c>
       <c r="G396" s="5" t="n">
         <v>0.047467</v>
@@ -47781,15 +47689,11 @@
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E397" s="5" t="n">
+        <v>0.111569</v>
+      </c>
+      <c r="F397" s="5" t="n">
+        <v>0.058285</v>
       </c>
       <c r="G397" s="5" t="n">
         <v>0.051205</v>
@@ -56553,15 +56457,11 @@
           <t>InterestIncomeNonOperating</t>
         </is>
       </c>
-      <c r="E487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E487" s="5" t="n">
+        <v>0.035292</v>
+      </c>
+      <c r="F487" s="5" t="n">
+        <v>0.000213</v>
       </c>
       <c r="G487" s="5" t="n">
         <v>0.000171</v>
@@ -56655,15 +56555,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F488" s="5" t="n">
+        <v>1.519418</v>
+      </c>
+      <c r="G488" s="5" t="n">
+        <v>0.06680700000000001</v>
       </c>
       <c r="H488" t="inlineStr">
         <is>
@@ -57343,15 +57239,11 @@
           <t>OperatingExpense</t>
         </is>
       </c>
-      <c r="E495" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F495" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E495" s="5" t="n">
+        <v>2.31641</v>
+      </c>
+      <c r="F495" s="5" t="n">
+        <v>4.029729</v>
       </c>
       <c r="G495" s="5" t="n">
         <v>1.063419</v>
@@ -57440,15 +57332,11 @@
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E496" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F496" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E496" s="5" t="n">
+        <v>-5.165861</v>
+      </c>
+      <c r="F496" s="5" t="n">
+        <v>-5.617992</v>
       </c>
       <c r="G496" s="5" t="n">
         <v>-2.445618</v>
@@ -57933,15 +57821,11 @@
           <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
-      <c r="E501" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E501" s="5" t="n">
+        <v>0.236798</v>
+      </c>
+      <c r="F501" s="5" t="n">
+        <v>0.302563</v>
       </c>
       <c r="G501" t="inlineStr">
         <is>
@@ -58034,15 +57918,11 @@
           <t>OtherOperatingExpenses</t>
         </is>
       </c>
-      <c r="E502" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F502" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E502" s="5" t="n">
+        <v>0.252046</v>
+      </c>
+      <c r="F502" s="5" t="n">
+        <v>0.110042</v>
       </c>
       <c r="G502" t="inlineStr">
         <is>
@@ -58140,10 +58020,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F503" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F503" s="5" t="n">
+        <v>-1.588263</v>
       </c>
       <c r="G503" s="5" t="n">
         <v>-1.382199</v>
@@ -58234,15 +58112,11 @@
           <t>OtherIncomeExpense</t>
         </is>
       </c>
-      <c r="E504" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F504" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E504" s="5" t="n">
+        <v>-1.173327</v>
+      </c>
+      <c r="F504" s="5" t="n">
+        <v>1.519418</v>
       </c>
       <c r="G504" s="5" t="n">
         <v>0.06680700000000001</v>
@@ -58427,7 +58301,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
           <t>-</t>
@@ -59332,7 +59210,11 @@
           <t>Director fees (Note 8a)</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>-</t>
@@ -60653,10 +60535,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F528" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F528" s="5" t="n">
+        <v>-5.153992</v>
       </c>
       <c r="G528" s="5" t="n">
         <v>-2.909618</v>
@@ -60756,10 +60636,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F529" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F529" s="5" t="n">
+        <v>-4.699999999999999e-07</v>
       </c>
       <c r="G529" s="5" t="n">
         <v>-1.3e-07</v>
@@ -60859,10 +60737,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F530" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F530" s="5" t="n">
+        <v>-4.3e-07</v>
       </c>
       <c r="G530" s="5" t="n">
         <v>-1.5e-07</v>
@@ -60962,10 +60838,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F531" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F531" s="5" t="n">
+        <v>11.896946</v>
       </c>
       <c r="G531" s="5" t="n">
         <v>19.162492</v>
@@ -61061,10 +60935,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F532" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F532" s="5" t="n">
+        <v>5e-06</v>
       </c>
       <c r="G532" s="5" t="n">
         <v>5e-06</v>
@@ -61135,6 +61007,3323 @@
         </is>
       </c>
       <c r="U532" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Consulting fees (Note 7e) $</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E533" s="5" t="n">
+        <v>0.037591</v>
+      </c>
+      <c r="F533" s="5" t="n">
+        <v>0.091308</v>
+      </c>
+      <c r="G533" s="5" t="n">
+        <v>0.015405</v>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U533" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Stock-based compensation (Note 10d)</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr"/>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F534" s="5" t="n">
+        <v>0.6973780000000001</v>
+      </c>
+      <c r="G534" s="5" t="n">
+        <v>0.640313</v>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U534" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E535" s="5" t="n">
+        <v>0.092375</v>
+      </c>
+      <c r="F535" s="5" t="n">
+        <v>0.028542</v>
+      </c>
+      <c r="G535" s="5" t="n">
+        <v>0.137891</v>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Promotion and shareholder relations (Note 7f)</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr"/>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F536" s="5" t="n">
+        <v>0.07688200000000001</v>
+      </c>
+      <c r="G536" s="5" t="n">
+        <v>0.047467</v>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U536" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Director fees (Note 7a)</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E537" s="5" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="F537" s="5" t="n">
+        <v>0.029666</v>
+      </c>
+      <c r="G537" s="5" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U537" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Professional fees (Notes 7b and 7c)</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F538" s="5" t="n">
+        <v>0.302563</v>
+      </c>
+      <c r="G538" s="5" t="n">
+        <v>0.203001</v>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U538" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Wages, salaries and benefits (Note 7d)</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F539" s="5" t="n">
+        <v>0.110042</v>
+      </c>
+      <c r="G539" s="5" t="n">
+        <v>0.07147000000000001</v>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U539" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Transfer and filing fees</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr"/>
+      <c r="E540" s="5" t="n">
+        <v>0.118248</v>
+      </c>
+      <c r="F540" s="5" t="n">
+        <v>0.151483</v>
+      </c>
+      <c r="G540" s="5" t="n">
+        <v>0.14213</v>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U540" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Amortization (Note 5)</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F541" s="5" t="n">
+        <v>0.010332</v>
+      </c>
+      <c r="G541" s="5" t="n">
+        <v>0.009708</v>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U541" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Accretion of asset retirement obligation (Note 9)</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr"/>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G542" s="5" t="n">
+        <v>0.003942</v>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U542" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Loss on sale of available-for-sale investments (Note 3)</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr"/>
+      <c r="E543" s="5" t="n">
+        <v>-0.002913</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G543" s="5" t="n">
+        <v>-0.214241</v>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U543" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Amortization of mining equipment (Note 5)</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr"/>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F544" s="5" t="n">
+        <v>-0.387811</v>
+      </c>
+      <c r="G544" s="5" t="n">
+        <v>-0.258867</v>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U544" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Write-off of accounts payable (Note 6)</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr"/>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G545" s="5" t="n">
+        <v>0.397556</v>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U545" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Interest, bank charges and loan arrangement fees (Note 8)</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr"/>
+      <c r="E546" s="5" t="n">
+        <v>-0.721494</v>
+      </c>
+      <c r="F546" s="5" t="n">
+        <v>-2.036144</v>
+      </c>
+      <c r="G546" s="5" t="n">
+        <v>-0.279815</v>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U546" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Write-off of property, plant and equipment (Note 5)</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr"/>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G547" s="5" t="n">
+        <v>-0.039248</v>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U547" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Loss on sale of mineral property</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr"/>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F548" s="5" t="n">
+        <v>-3.081458</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U548" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Loss on sale of property, plant and equipment (Note 5)</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr"/>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F549" s="5" t="n">
+        <v>-0.043947</v>
+      </c>
+      <c r="G549" s="5" t="n">
+        <v>-0.078044</v>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U549" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income (Loss)</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Unrealized (loss) gain on available-for-sale investments (Note 3)</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr"/>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F550" s="5" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="G550" s="5" t="n">
+        <v>-0.678241</v>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U550" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income (Loss)</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>(Note 3)</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr"/>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G551" s="5" t="n">
+        <v>0.214241</v>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U551" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Consulting fees – Stock-based compensation (Note 10d)</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr"/>
+      <c r="E552" s="5" t="n">
+        <v>0.307331</v>
+      </c>
+      <c r="F552" s="5" t="n">
+        <v>0.086116</v>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U552" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Director fees – Stock-based compensation (Note 10d)</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr"/>
+      <c r="E553" s="5" t="n">
+        <v>0.285955</v>
+      </c>
+      <c r="F553" s="5" t="n">
+        <v>0.253651</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U553" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Wages – Stock-based compensation (Note 10d)</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr"/>
+      <c r="E554" s="5" t="n">
+        <v>1.019599</v>
+      </c>
+      <c r="F554" s="5" t="n">
+        <v>0.312012</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U554" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Shareholder relations – Stock-based compensation (Note 10d)</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr"/>
+      <c r="E555" s="5" t="n">
+        <v>0.028138</v>
+      </c>
+      <c r="F555" s="5" t="n">
+        <v>0.045599</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E556" s="5" t="n">
+        <v>0.019161</v>
+      </c>
+      <c r="F556" s="5" t="n">
+        <v>0.010332</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>General and Administrative Expenses</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Loss Before the Undernoted</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr"/>
+      <c r="E557" s="5" t="n">
+        <v>-2.849451</v>
+      </c>
+      <c r="F557" s="5" t="n">
+        <v>-1.588263</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Amortization of mining equipment</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr"/>
+      <c r="E558" s="5" t="n">
+        <v>-0.453968</v>
+      </c>
+      <c r="F558" s="5" t="n">
+        <v>-0.387811</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Other Income (Expenses)</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Loss on sale of capital assets</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr"/>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F559" s="5" t="n">
+        <v>-0.043947</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Unrealized gain on available-for-sale investments (Note 3)</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr"/>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F560" s="5" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Comprehensive Loss for the Year $</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E561" s="5" t="n">
+        <v>-5.165861</v>
+      </c>
+      <c r="F561" s="5" t="n">
+        <v>-5.153992</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Loss per Share – Basic and Diluted $</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E562" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="F562" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Comprehensive Loss per Share – Basic and Diluted $</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E563" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="F563" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E564" s="5" t="n">
+        <v>63.687408</v>
+      </c>
+      <c r="F564" s="5" t="n">
+        <v>71.38167300000001</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Other Comprehensive Income</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>- See Accompanying Notes</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr"/>
+      <c r="E565" s="5" t="n">
+        <v>5e-06</v>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T565" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U565" t="inlineStr">
         <is>
           <t>-</t>
         </is>
